--- a/Daily_Report/Top 7 broker List with its Turnover 2024-04-28.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-04-28.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="277">
   <si>
     <t>Date: 2024-04-28</t>
   </si>
@@ -59,25 +59,28 @@
     <t>7</t>
   </si>
   <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
+    <t>Linch Stock Market Limited</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
+    <t>45</t>
   </si>
   <si>
     <t>58</t>
@@ -86,82 +89,79 @@
     <t>34</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
     <t>38</t>
   </si>
   <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>323,922,447.5</t>
-  </si>
-  <si>
-    <t>257,112,795.4</t>
-  </si>
-  <si>
-    <t>242,002,986.1</t>
-  </si>
-  <si>
-    <t>185,883,050.2</t>
-  </si>
-  <si>
-    <t>167,057,899.7</t>
-  </si>
-  <si>
-    <t>159,662,044.19</t>
-  </si>
-  <si>
-    <t>150,778,049.8</t>
-  </si>
-  <si>
-    <t>176,203,536.9</t>
-  </si>
-  <si>
-    <t>93,743,267.4</t>
-  </si>
-  <si>
-    <t>108,658,922.6</t>
-  </si>
-  <si>
-    <t>61,971,866.8</t>
-  </si>
-  <si>
-    <t>132,741,921.6</t>
-  </si>
-  <si>
-    <t>61,788,073.1</t>
-  </si>
-  <si>
-    <t>140,949,891.4</t>
-  </si>
-  <si>
-    <t>147,718,910.6</t>
-  </si>
-  <si>
-    <t>163,369,528.0</t>
-  </si>
-  <si>
-    <t>133,344,063.5</t>
-  </si>
-  <si>
-    <t>123,911,183.4</t>
-  </si>
-  <si>
-    <t>34,315,978.1</t>
-  </si>
-  <si>
-    <t>97,873,971.1</t>
-  </si>
-  <si>
-    <t>9,828,158.4</t>
+    <t>351,663,132.3</t>
+  </si>
+  <si>
+    <t>297,910,224.5</t>
+  </si>
+  <si>
+    <t>251,738,786.44</t>
+  </si>
+  <si>
+    <t>189,253,752.8</t>
+  </si>
+  <si>
+    <t>145,758,448.69</t>
+  </si>
+  <si>
+    <t>143,365,833.3</t>
+  </si>
+  <si>
+    <t>142,764,230.69</t>
+  </si>
+  <si>
+    <t>185,439,687.4</t>
+  </si>
+  <si>
+    <t>145,308,459.69</t>
+  </si>
+  <si>
+    <t>143,508,183.32</t>
+  </si>
+  <si>
+    <t>102,411,515.7</t>
+  </si>
+  <si>
+    <t>85,658,254.7</t>
+  </si>
+  <si>
+    <t>62,311,976.4</t>
+  </si>
+  <si>
+    <t>68,591,712.8</t>
+  </si>
+  <si>
+    <t>166,223,444.9</t>
+  </si>
+  <si>
+    <t>152,601,764.8</t>
+  </si>
+  <si>
+    <t>108,230,603.12</t>
+  </si>
+  <si>
+    <t>86,842,237.1</t>
+  </si>
+  <si>
+    <t>60,100,194.0</t>
+  </si>
+  <si>
+    <t>81,053,856.9</t>
+  </si>
+  <si>
+    <t>74,172,517.9</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,376 +179,334 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>SADBL</t>
-  </si>
-  <si>
-    <t>59,844,900.0</t>
-  </si>
-  <si>
-    <t>RSDC</t>
-  </si>
-  <si>
-    <t>18,700,867.5</t>
+    <t>UAIL</t>
+  </si>
+  <si>
+    <t>26,100,000.0</t>
+  </si>
+  <si>
+    <t>PPL</t>
+  </si>
+  <si>
+    <t>19,156,360.0</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>17,268,984.0</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>14,800,673.0</t>
+  </si>
+  <si>
+    <t>ILI</t>
+  </si>
+  <si>
+    <t>13,365,965.0</t>
+  </si>
+  <si>
+    <t>CHCL</t>
+  </si>
+  <si>
+    <t>9,571,228.6</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>7,199,831.5</t>
+  </si>
+  <si>
+    <t>6,695,920.7</t>
+  </si>
+  <si>
+    <t>MEHL</t>
+  </si>
+  <si>
+    <t>5,924,932.6</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>5,851,187.5</t>
+  </si>
+  <si>
+    <t>SIFC</t>
+  </si>
+  <si>
+    <t>15,685,089.1</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>12,172,138.0</t>
+  </si>
+  <si>
+    <t>GMFIL</t>
+  </si>
+  <si>
+    <t>9,267,881.0</t>
+  </si>
+  <si>
+    <t>CYCL</t>
+  </si>
+  <si>
+    <t>8,070,030.0</t>
+  </si>
+  <si>
+    <t>PFL</t>
+  </si>
+  <si>
+    <t>7,470,631.2</t>
+  </si>
+  <si>
+    <t>33,192,020.5</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>11,331,805.1</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>3,908,585.0</t>
+  </si>
+  <si>
+    <t>NIMB</t>
+  </si>
+  <si>
+    <t>2,801,836.4</t>
+  </si>
+  <si>
+    <t>GUFL</t>
+  </si>
+  <si>
+    <t>2,744,895.0</t>
+  </si>
+  <si>
+    <t>38,790,479.9</t>
+  </si>
+  <si>
+    <t>6,910,590.9</t>
+  </si>
+  <si>
+    <t>CFCL</t>
+  </si>
+  <si>
+    <t>3,696,219.0</t>
+  </si>
+  <si>
+    <t>KKHC</t>
+  </si>
+  <si>
+    <t>3,672,127.5</t>
+  </si>
+  <si>
+    <t>3,030,580.0</t>
+  </si>
+  <si>
+    <t>CHL</t>
+  </si>
+  <si>
+    <t>3,208,323.0</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>2,774,926.0</t>
+  </si>
+  <si>
+    <t>2,695,459.0</t>
+  </si>
+  <si>
+    <t>1,892,004.0</t>
+  </si>
+  <si>
+    <t>1,861,267.5</t>
+  </si>
+  <si>
+    <t>3,743,208.0</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>3,510,956.2</t>
+  </si>
+  <si>
+    <t>MPFL</t>
+  </si>
+  <si>
+    <t>3,496,210.6</t>
+  </si>
+  <si>
+    <t>UPCL</t>
+  </si>
+  <si>
+    <t>2,615,734.6</t>
+  </si>
+  <si>
+    <t>SONA</t>
+  </si>
+  <si>
+    <t>2,349,708.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>26,275,187.0</t>
+  </si>
+  <si>
+    <t>14,706,267.0</t>
+  </si>
+  <si>
+    <t>10,023,751.0</t>
   </si>
   <si>
     <t>AVYAN</t>
   </si>
   <si>
-    <t>16,424,770.0</t>
-  </si>
-  <si>
-    <t>JBBL</t>
-  </si>
-  <si>
-    <t>12,817,027.6</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>9,641,830.0</t>
-  </si>
-  <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>27,961,104.0</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>13,985,510.0</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>13,927,430.0</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>7,734,560.0</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>6,804,195.2</t>
+    <t>8,219,648.0</t>
+  </si>
+  <si>
+    <t>11,555,096.1</t>
+  </si>
+  <si>
+    <t>9,180,246.8</t>
+  </si>
+  <si>
+    <t>PROFL</t>
+  </si>
+  <si>
+    <t>9,155,986.3</t>
+  </si>
+  <si>
+    <t>9,029,288.0</t>
+  </si>
+  <si>
+    <t>MKHL</t>
+  </si>
+  <si>
+    <t>6,234,794.7</t>
+  </si>
+  <si>
+    <t>18,675,328.59</t>
   </si>
   <si>
     <t>SFCL</t>
   </si>
   <si>
-    <t>27,483,843.4</t>
-  </si>
-  <si>
-    <t>11,011,132.0</t>
-  </si>
-  <si>
-    <t>EBL</t>
-  </si>
-  <si>
-    <t>10,404,270.0</t>
-  </si>
-  <si>
-    <t>GMFIL</t>
-  </si>
-  <si>
-    <t>10,051,110.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>8,769,600.0</t>
-  </si>
-  <si>
-    <t>15,689,451.9</t>
-  </si>
-  <si>
-    <t>RBCL</t>
-  </si>
-  <si>
-    <t>11,266,500.0</t>
-  </si>
-  <si>
-    <t>MKCL</t>
-  </si>
-  <si>
-    <t>7,421,100.0</t>
-  </si>
-  <si>
-    <t>ULHC</t>
-  </si>
-  <si>
-    <t>5,484,040.0</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>5,253,192.0</t>
-  </si>
-  <si>
-    <t>35,884,020.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>24,116,400.0</t>
-  </si>
-  <si>
-    <t>GUFL</t>
-  </si>
-  <si>
-    <t>23,961,300.0</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>18,034,008.0</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>10,152,900.0</t>
-  </si>
-  <si>
-    <t>CHL</t>
-  </si>
-  <si>
-    <t>28,231,500.0</t>
-  </si>
-  <si>
-    <t>12,662,850.0</t>
-  </si>
-  <si>
-    <t>JBLB</t>
-  </si>
-  <si>
-    <t>2,599,409.19</t>
-  </si>
-  <si>
-    <t>GCIL</t>
-  </si>
-  <si>
-    <t>2,443,308.0</t>
-  </si>
-  <si>
-    <t>SGHC</t>
-  </si>
-  <si>
-    <t>1,587,650.0</t>
-  </si>
-  <si>
-    <t>PRIN</t>
-  </si>
-  <si>
-    <t>92,267,839.7</t>
-  </si>
-  <si>
-    <t>CFCL</t>
-  </si>
-  <si>
-    <t>23,251,800.0</t>
-  </si>
-  <si>
-    <t>ILBS</t>
-  </si>
-  <si>
-    <t>9,278,939.4</t>
-  </si>
-  <si>
-    <t>SNLI</t>
-  </si>
-  <si>
-    <t>4,607,960.0</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>3,885,420.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>64,130,298.0</t>
-  </si>
-  <si>
-    <t>MANDU</t>
-  </si>
-  <si>
-    <t>32,748,511.5</t>
-  </si>
-  <si>
-    <t>LBBLD89</t>
-  </si>
-  <si>
-    <t>9,674,400.0</t>
-  </si>
-  <si>
-    <t>JOSHI</t>
-  </si>
-  <si>
-    <t>5,835,331.0</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>5,346,637.2</t>
-  </si>
-  <si>
-    <t>38,280,000.0</t>
-  </si>
-  <si>
-    <t>37,303,924.0</t>
-  </si>
-  <si>
-    <t>22,607,211.0</t>
-  </si>
-  <si>
-    <t>SPHL</t>
-  </si>
-  <si>
-    <t>20,062,200.0</t>
+    <t>8,647,280.69</t>
   </si>
   <si>
     <t>SARBTM</t>
   </si>
   <si>
-    <t>8,276,710.0</t>
-  </si>
-  <si>
-    <t>26,517,987.0</t>
-  </si>
-  <si>
-    <t>21,090,470.4</t>
-  </si>
-  <si>
-    <t>17,840,568.0</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>7,432,017.4</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>7,292,757.5</t>
-  </si>
-  <si>
-    <t>87,606,365.0</t>
-  </si>
-  <si>
-    <t>GBBL</t>
-  </si>
-  <si>
-    <t>10,713,876.0</t>
-  </si>
-  <si>
-    <t>RADHI</t>
-  </si>
-  <si>
-    <t>5,950,800.0</t>
-  </si>
-  <si>
-    <t>3,132,939.6</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>1,948,737.8</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>14,607,300.0</t>
-  </si>
-  <si>
-    <t>7,814,800.0</t>
-  </si>
-  <si>
-    <t>2,626,156.0</t>
+    <t>8,096,096.8</t>
+  </si>
+  <si>
+    <t>6,972,475.0</t>
+  </si>
+  <si>
+    <t>4,130,967.0</t>
+  </si>
+  <si>
+    <t>10,646,999.0</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>8,804,470.0</t>
+  </si>
+  <si>
+    <t>ULBSL</t>
+  </si>
+  <si>
+    <t>8,552,994.19</t>
+  </si>
+  <si>
+    <t>8,397,959.0</t>
   </si>
   <si>
     <t>NFS</t>
   </si>
   <si>
-    <t>2,280,315.0</t>
-  </si>
-  <si>
-    <t>LEC</t>
-  </si>
-  <si>
-    <t>796,682.9</t>
-  </si>
-  <si>
-    <t>SICL</t>
-  </si>
-  <si>
-    <t>26,998,840.5</t>
-  </si>
-  <si>
-    <t>17,949,389.0</t>
-  </si>
-  <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>17,424,534.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>16,636,039.5</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>3,764,034.0</t>
-  </si>
-  <si>
-    <t>RBCLPO</t>
-  </si>
-  <si>
-    <t>1,429,720.0</t>
-  </si>
-  <si>
-    <t>MERO</t>
-  </si>
-  <si>
-    <t>1,193,750.0</t>
-  </si>
-  <si>
-    <t>ACLBSL</t>
-  </si>
-  <si>
-    <t>859,673.1</t>
-  </si>
-  <si>
-    <t>SPIL</t>
-  </si>
-  <si>
-    <t>718,340.0</t>
-  </si>
-  <si>
-    <t>516,555.0</t>
+    <t>3,754,557.0</t>
+  </si>
+  <si>
+    <t>19,296,629.0</t>
+  </si>
+  <si>
+    <t>11,721,465.5</t>
+  </si>
+  <si>
+    <t>4,485,077.9</t>
+  </si>
+  <si>
+    <t>CORBL</t>
+  </si>
+  <si>
+    <t>1,764,020.0</t>
+  </si>
+  <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>1,651,164.2</t>
+  </si>
+  <si>
+    <t>13,941,841.8</t>
+  </si>
+  <si>
+    <t>7,496,644.9</t>
+  </si>
+  <si>
+    <t>ALBSL</t>
+  </si>
+  <si>
+    <t>2,787,859.3</t>
+  </si>
+  <si>
+    <t>VLUCL</t>
+  </si>
+  <si>
+    <t>2,747,218.0</t>
+  </si>
+  <si>
+    <t>2,073,736.2</t>
+  </si>
+  <si>
+    <t>5,072,157.3</t>
+  </si>
+  <si>
+    <t>TRH</t>
+  </si>
+  <si>
+    <t>4,459,487.0</t>
+  </si>
+  <si>
+    <t>3,934,895.3</t>
+  </si>
+  <si>
+    <t>USLB</t>
+  </si>
+  <si>
+    <t>2,896,798.2</t>
+  </si>
+  <si>
+    <t>2,754,999.1</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -566,109 +524,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>166,214,025.5</t>
-  </si>
-  <si>
-    <t>126,468,882.0</t>
-  </si>
-  <si>
-    <t>111,168,733.2</t>
-  </si>
-  <si>
-    <t>101,222,470.0</t>
-  </si>
-  <si>
-    <t>92,275,588.7</t>
+    <t>135,951,431.6</t>
+  </si>
+  <si>
+    <t>91,476,001.7</t>
+  </si>
+  <si>
+    <t>91,243,013.8</t>
+  </si>
+  <si>
+    <t>86,908,485.4</t>
+  </si>
+  <si>
+    <t>76,370,268.0</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>859,282,545.3</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>895,625,062.4</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>359,254,555.5</t>
+    <t>574,952,452.12</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>291,133,719.7</t>
+    <t>458,405,140.4</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>253,504,515.9</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>274,374,083.7</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>214,529,657.3</t>
+    <t>172,068,154.0</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>167,008,074.0</t>
+    <t>154,588,248.0</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>49,505,869.9</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>45,910,636.8</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>153,009,559.5</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>61,586,608.2</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>54,117,610.1</t>
+    <t>30,427,728.9</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>12,130,320.0</t>
+    <t>25,103,826.4</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>20,248,530.0</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>15,219,450.2</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>3,499,300.0</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>2,429,243.6</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>2,197,783.2</t>
+    <t>6,081,877.0</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>995,091.0</t>
+    <t>1,243,357.55</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>36,720.0</t>
+    <t>616,056.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -680,205 +638,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>81,096,252.0</t>
-  </si>
-  <si>
-    <t>37,478,060.0</t>
-  </si>
-  <si>
-    <t>20,079,507.8</t>
-  </si>
-  <si>
-    <t>14,559,357.0</t>
-  </si>
-  <si>
-    <t>9,796,797.69</t>
-  </si>
-  <si>
-    <t>44,068,657.0</t>
-  </si>
-  <si>
-    <t>29,125,885.8</t>
-  </si>
-  <si>
-    <t>6,198,334.2</t>
-  </si>
-  <si>
-    <t>5,848,025.0</t>
-  </si>
-  <si>
-    <t>4,652,853.9</t>
-  </si>
-  <si>
-    <t>52,204,123.3</t>
-  </si>
-  <si>
-    <t>16,339,988.3</t>
-  </si>
-  <si>
-    <t>10,681,769.19</t>
-  </si>
-  <si>
-    <t>8,279,414.3</t>
-  </si>
-  <si>
-    <t>19,755,855.2</t>
-  </si>
-  <si>
-    <t>17,816,440.5</t>
-  </si>
-  <si>
-    <t>4,291,006.5</t>
-  </si>
-  <si>
-    <t>3,902,855.7</t>
-  </si>
-  <si>
-    <t>63,310,466.4</t>
-  </si>
-  <si>
-    <t>30,474,531.0</t>
-  </si>
-  <si>
-    <t>22,320,305.7</t>
-  </si>
-  <si>
-    <t>11,886,763.5</t>
-  </si>
-  <si>
-    <t>2,043,815.2</t>
-  </si>
-  <si>
-    <t>32,250,902.3</t>
-  </si>
-  <si>
-    <t>14,727,093.8</t>
-  </si>
-  <si>
-    <t>8,092,702.5</t>
-  </si>
-  <si>
-    <t>2,881,626.6</t>
-  </si>
-  <si>
-    <t>2,705,864.2</t>
-  </si>
-  <si>
-    <t>26,725,430.0</t>
-  </si>
-  <si>
-    <t>10,650,735.3</t>
-  </si>
-  <si>
-    <t>10,046,664.4</t>
-  </si>
-  <si>
-    <t>476,155.0</t>
-  </si>
-  <si>
-    <t>65,779,112.7</t>
-  </si>
-  <si>
-    <t>57,352,919.8</t>
-  </si>
-  <si>
-    <t>17,495,566.0</t>
-  </si>
-  <si>
-    <t>5,197,335.3</t>
-  </si>
-  <si>
-    <t>1,521,748.2</t>
-  </si>
-  <si>
-    <t>87,687,972.9</t>
-  </si>
-  <si>
-    <t>43,352,270.2</t>
-  </si>
-  <si>
-    <t>7,843,363.0</t>
-  </si>
-  <si>
-    <t>7,286,574.0</t>
-  </si>
-  <si>
-    <t>7,247,693.5</t>
-  </si>
-  <si>
-    <t>41,140,706.29</t>
-  </si>
-  <si>
-    <t>27,580,031.1</t>
-  </si>
-  <si>
-    <t>27,055,820.0</t>
-  </si>
-  <si>
-    <t>16,298,934.2</t>
-  </si>
-  <si>
-    <t>9,655,190.69</t>
-  </si>
-  <si>
-    <t>87,655,590.0</t>
-  </si>
-  <si>
-    <t>12,257,189.1</t>
-  </si>
-  <si>
-    <t>8,394,343.0</t>
-  </si>
-  <si>
-    <t>6,745,316.6</t>
-  </si>
-  <si>
-    <t>4,415,859.7</t>
-  </si>
-  <si>
-    <t>14,758,200.0</t>
-  </si>
-  <si>
-    <t>13,339,551.0</t>
-  </si>
-  <si>
-    <t>2,645,119.6</t>
-  </si>
-  <si>
-    <t>1,898,307.5</t>
-  </si>
-  <si>
-    <t>636,810.0</t>
-  </si>
-  <si>
-    <t>60,895,720.4</t>
-  </si>
-  <si>
-    <t>28,255,851.9</t>
-  </si>
-  <si>
-    <t>4,110,890.9</t>
-  </si>
-  <si>
-    <t>2,213,480.4</t>
-  </si>
-  <si>
-    <t>671,483.4</t>
-  </si>
-  <si>
-    <t>5,232,052.2</t>
-  </si>
-  <si>
-    <t>2,322,738.5</t>
-  </si>
-  <si>
-    <t>1,305,802.8</t>
-  </si>
-  <si>
-    <t>503,110.0</t>
-  </si>
-  <si>
-    <t>288,014.0</t>
+    <t>81,156,421.0</t>
+  </si>
+  <si>
+    <t>33,737,176.79</t>
+  </si>
+  <si>
+    <t>29,557,444.0</t>
+  </si>
+  <si>
+    <t>19,869,818.39</t>
+  </si>
+  <si>
+    <t>5,525,177.8</t>
+  </si>
+  <si>
+    <t>33,462,287.7</t>
+  </si>
+  <si>
+    <t>32,632,823.9</t>
+  </si>
+  <si>
+    <t>25,865,272.4</t>
+  </si>
+  <si>
+    <t>24,353,497.2</t>
+  </si>
+  <si>
+    <t>7,883,241.4</t>
+  </si>
+  <si>
+    <t>68,341,464.5</t>
+  </si>
+  <si>
+    <t>23,988,303.52</t>
+  </si>
+  <si>
+    <t>18,827,914.8</t>
+  </si>
+  <si>
+    <t>12,133,631.1</t>
+  </si>
+  <si>
+    <t>7,137,443.7</t>
+  </si>
+  <si>
+    <t>42,035,216.5</t>
+  </si>
+  <si>
+    <t>26,115,831.0</t>
+  </si>
+  <si>
+    <t>10,000,812.4</t>
+  </si>
+  <si>
+    <t>8,356,260.0</t>
+  </si>
+  <si>
+    <t>6,372,135.5</t>
+  </si>
+  <si>
+    <t>56,993,033.5</t>
+  </si>
+  <si>
+    <t>11,341,945.8</t>
+  </si>
+  <si>
+    <t>9,650,047.5</t>
+  </si>
+  <si>
+    <t>2,114,218.0</t>
+  </si>
+  <si>
+    <t>1,661,983.3</t>
+  </si>
+  <si>
+    <t>16,066,941.1</t>
+  </si>
+  <si>
+    <t>15,777,201.1</t>
+  </si>
+  <si>
+    <t>12,843,323.9</t>
+  </si>
+  <si>
+    <t>7,075,644.1</t>
+  </si>
+  <si>
+    <t>3,713,689.8</t>
+  </si>
+  <si>
+    <t>21,341,256.89</t>
+  </si>
+  <si>
+    <t>17,372,942.8</t>
+  </si>
+  <si>
+    <t>12,754,672.7</t>
+  </si>
+  <si>
+    <t>5,504,379.6</t>
+  </si>
+  <si>
+    <t>3,994,692.1</t>
+  </si>
+  <si>
+    <t>61,723,351.7</t>
+  </si>
+  <si>
+    <t>34,729,175.79</t>
+  </si>
+  <si>
+    <t>22,903,765.5</t>
+  </si>
+  <si>
+    <t>15,322,652.7</t>
+  </si>
+  <si>
+    <t>10,301,078.0</t>
+  </si>
+  <si>
+    <t>43,196,296.4</t>
+  </si>
+  <si>
+    <t>37,225,511.2</t>
+  </si>
+  <si>
+    <t>34,262,106.9</t>
+  </si>
+  <si>
+    <t>20,626,189.1</t>
+  </si>
+  <si>
+    <t>10,899,779.1</t>
+  </si>
+  <si>
+    <t>43,484,078.1</t>
+  </si>
+  <si>
+    <t>33,402,102.2</t>
+  </si>
+  <si>
+    <t>8,146,390.6</t>
+  </si>
+  <si>
+    <t>7,569,018.3</t>
+  </si>
+  <si>
+    <t>6,714,510.2</t>
+  </si>
+  <si>
+    <t>42,828,863.4</t>
+  </si>
+  <si>
+    <t>13,514,753.6</t>
+  </si>
+  <si>
+    <t>10,154,854.1</t>
+  </si>
+  <si>
+    <t>9,082,036.19</t>
+  </si>
+  <si>
+    <t>2,899,798.5</t>
+  </si>
+  <si>
+    <t>41,000,297.4</t>
+  </si>
+  <si>
+    <t>4,262,625.4</t>
+  </si>
+  <si>
+    <t>3,679,145.2</t>
+  </si>
+  <si>
+    <t>3,483,550.7</t>
+  </si>
+  <si>
+    <t>2,206,404.79</t>
+  </si>
+  <si>
+    <t>34,170,754.0</t>
+  </si>
+  <si>
+    <t>18,472,902.3</t>
+  </si>
+  <si>
+    <t>8,723,904.69</t>
+  </si>
+  <si>
+    <t>8,357,715.4</t>
+  </si>
+  <si>
+    <t>3,422,568.8</t>
+  </si>
+  <si>
+    <t>24,504,342.6</t>
+  </si>
+  <si>
+    <t>13,721,556.6</t>
+  </si>
+  <si>
+    <t>8,535,207.9</t>
+  </si>
+  <si>
+    <t>8,090,191.6</t>
+  </si>
+  <si>
+    <t>5,054,757.0</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1654,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.18475070333</v>
+        <v>0.0742187554017871</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1696,52 +1663,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1087503403185355</v>
+        <v>0.03212789563051737</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="J9" s="14">
+        <v>0.06230700211839791</v>
+      </c>
+      <c r="K9" s="15" t="s">
         <v>75</v>
-      </c>
-      <c r="J9" s="14">
-        <v>0.1135681994793369</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>68</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>83</v>
       </c>
       <c r="M9" s="16">
-        <v>0.08440496259943556</v>
+        <v>0.1753836846505059</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="O9" s="17" t="s">
         <v>92</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2147998991034843</v>
+        <v>0.2661285177357956</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1768203591621058</v>
+        <v>0.0223785746307241</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="V9" s="18">
-        <v>0.6119447746033919</v>
+        <v>0.02621950877783843</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1753,7 +1720,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.05773254568904182</v>
+        <v>0.05447360908921756</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1762,16 +1729,16 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.054394453524735</v>
+        <v>0.02416778917905182</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>76</v>
       </c>
       <c r="J10" s="14">
-        <v>0.04549998401858563</v>
+        <v>0.04835225501852149</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>84</v>
@@ -1780,34 +1747,34 @@
         <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.06061069036621609</v>
+        <v>0.05987625044336769</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>94</v>
-      </c>
       <c r="P10" s="18">
-        <v>0.1443595306974879</v>
+        <v>0.04741125445306692</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S10" s="16">
-        <v>0.07931033367039905</v>
+        <v>0.01935556008099456</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1542121020323742</v>
+        <v>0.02459268811792084</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1819,16 +1786,16 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.05070587150339434</v>
+        <v>0.04910660917752395</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.0541685604496368</v>
+        <v>0.02247630376311572</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>77</v>
@@ -1837,7 +1804,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="14">
-        <v>0.04299232074640917</v>
+        <v>0.03681546706037263</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>86</v>
@@ -1846,34 +1813,34 @@
         <v>87</v>
       </c>
       <c r="M11" s="16">
-        <v>0.03992348948446511</v>
+        <v>0.02065261556070977</v>
       </c>
       <c r="N11" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="O11" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="P11" s="18">
-        <v>0.1434311100703967</v>
+        <v>0.02535852317972701</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01628069597270007</v>
+        <v>0.01880126483385773</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="V11" s="18">
-        <v>0.06154038609935648</v>
+        <v>0.02448940174200091</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1885,16 +1852,16 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03956819818731457</v>
+        <v>0.04208764479574079</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.03008236127636921</v>
+        <v>0.01988831571640134</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>79</v>
@@ -1903,7 +1870,7 @@
         <v>80</v>
       </c>
       <c r="J12" s="14">
-        <v>0.04153299991036764</v>
+        <v>0.03205715779488525</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>88</v>
@@ -1912,34 +1879,34 @@
         <v>89</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02950263616881407</v>
+        <v>0.0148046543782988</v>
       </c>
       <c r="N12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>98</v>
-      </c>
       <c r="P12" s="18">
-        <v>0.1079506448505889</v>
+        <v>0.02519323945027689</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01530299835657497</v>
+        <v>0.01319703555895978</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03056121236554155</v>
+        <v>0.01832205859391081</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1951,16 +1918,16 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02976585931112415</v>
+        <v>0.03800786540397883</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.02646385291488297</v>
+        <v>0.01964077436355327</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>81</v>
@@ -1969,7 +1936,7 @@
         <v>82</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03623756938427299</v>
+        <v>0.02967612303867433</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>90</v>
@@ -1978,34 +1945,34 @@
         <v>91</v>
       </c>
       <c r="M13" s="16">
-        <v>0.0282607370298037</v>
+        <v>0.01450378108433472</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P13" s="18">
-        <v>0.06077473749060906</v>
+        <v>0.02079179647580868</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="S13" s="16">
-        <v>0.009943816064456979</v>
+        <v>0.01298264347339444</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02576913552837317</v>
+        <v>0.01645866046753405</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2016,7 +1983,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2025,7 +1992,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2034,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2043,7 +2010,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2052,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2061,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2070,7 +2037,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2079,566 +2046,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.07471692249383971</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="10">
-        <v>0.1979804070231965</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>130</v>
-      </c>
       <c r="G16" s="12">
-        <v>0.1488840722238128</v>
+        <v>0.03878717529548906</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1095771065776944</v>
+        <v>0.07418534451563791</v>
       </c>
       <c r="K16" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.05625779590881645</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.1323877220984721</v>
+      </c>
+      <c r="Q16" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.4712982969977109</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.08743854691236728</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>160</v>
-      </c>
       <c r="R16" s="15" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1690999300132974</v>
+        <v>0.0972466136392903</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="V16" s="18">
-        <v>0.009482282082149599</v>
+        <v>0.03552820811718912</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.04910660917752395</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="G17" s="12">
+        <v>0.03081548078924697</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.0343502120681789</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.04652203652365302</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="O17" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.08041705715546629</v>
+      </c>
+      <c r="Q17" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="10">
-        <v>0.1010998519946661</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0.1450877773000946</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.08714962877063442</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0.05763772430284771</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="O17" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="P17" s="18">
-        <v>0.04677899108053972</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>99</v>
-      </c>
       <c r="R17" s="15" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1124211398515966</v>
+        <v>0.0522903172076774</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="V17" s="18">
-        <v>0.007917266482644212</v>
+        <v>0.03123672490044805</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.04181918901710243</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.02986640806978961</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="11" t="s">
+      <c r="G18" s="12">
+        <v>0.03073404518212499</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I18" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="G18" s="12">
-        <v>0.08792721095357824</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I18" s="13" t="s">
+      <c r="J18" s="14">
+        <v>0.03216070481030003</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="L18" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="J18" s="14">
-        <v>0.07372044571643407</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>148</v>
-      </c>
       <c r="M18" s="16">
-        <v>0.03201367738261915</v>
+        <v>0.04519326075947699</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01572003481856296</v>
+        <v>0.03077062043402497</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="S18" s="16">
-        <v>0.1091338526154233</v>
+        <v>0.01944577195157976</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="V18" s="18">
-        <v>0.005701579912595473</v>
+        <v>0.02756219313974141</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01801459282935308</v>
+        <v>0.0285038438190582</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.03030875497863283</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.07802878876093461</v>
-      </c>
-      <c r="H19" s="13" t="s">
+      <c r="J19" s="14">
+        <v>0.02769726150905171</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="J19" s="14">
-        <v>0.03071043675853221</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>149</v>
-      </c>
       <c r="M19" s="16">
-        <v>0.0168543586767547</v>
+        <v>0.04437406854951412</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="P19" s="18">
-        <v>0.0136498483705048</v>
+        <v>0.01210235163541501</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="S19" s="16">
-        <v>0.1041953307272011</v>
+        <v>0.0191622922753939</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="V19" s="18">
-        <v>0.004764221323679702</v>
+        <v>0.02029078422372643</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.02337364154792293</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.02092843476743444</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.0164097358949674</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.01983874530597948</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.01132808571116468</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.01446464720545101</v>
+      </c>
+      <c r="T20" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D20" s="10">
-        <v>0.0165059175159511</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.03219096889800296</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.03013498972688916</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.01048367668759075</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.004768902885949547</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.02357500819221003</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>116</v>
-      </c>
       <c r="U20" s="17" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="V20" s="18">
-        <v>0.00342592970717678</v>
+        <v>0.01929754453543243</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="D31" s="22">
-        <v>0.3338661810969067</v>
+        <v>0.3203186176074351</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1339209358043661</v>
+        <v>0.214327610470413</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1085272255828917</v>
+        <v>0.1708817451026026</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1022796607225471</v>
+        <v>0.09450001810752486</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07997118484251467</v>
+        <v>0.06414261935729239</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="D36" s="22">
-        <v>0.06225635058638753</v>
+        <v>0.05762655621082979</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D37" s="22">
-        <v>0.05703806140115551</v>
+        <v>0.01845452569304218</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02295791682218723</v>
+        <v>0.0171143144867661</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D39" s="22">
-        <v>0.0201736648210375</v>
+        <v>0.01134268130022238</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="D40" s="22">
-        <v>0.004521873922365385</v>
+        <v>0.009358066229889045</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D41" s="22">
-        <v>0.001304449793289311</v>
+        <v>0.007548135562230275</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D42" s="22">
-        <v>0.0009055600582600464</v>
+        <v>0.005673422875251323</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D43" s="22">
-        <v>0.0008192775243433599</v>
+        <v>0.002267168632429632</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0003709445458388973</v>
+        <v>0.0004634919838488279</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D45" s="22">
-        <v>1.368827948720701E-05</v>
+        <v>0.000229649964808573</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -3017,331 +2984,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2503569994172756</v>
+        <v>0.2307788720108605</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1713981481607741</v>
+        <v>0.1123233945936622</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="J9" s="14">
-        <v>0.2157168559830428</v>
+        <v>0.2714776910878954</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1062811008251897</v>
+        <v>0.2221103459143665</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="P9" s="18">
-        <v>0.3789731973985783</v>
+        <v>0.3910101541853196</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="S9" s="16">
-        <v>0.201994797583833</v>
+        <v>0.1120695268194001</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>111</v>
+        <v>237</v>
       </c>
       <c r="V9" s="18">
-        <v>0.6119447746033919</v>
+        <v>0.1494860217812248</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1157007187654076</v>
+        <v>0.09593606409448453</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1132805769339008</v>
+        <v>0.1095391202325115</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="J10" s="14">
-        <v>0.0675197796660576</v>
+        <v>0.09529045507541377</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="M10" s="16">
-        <v>0.09584757986718254</v>
+        <v>0.1379937285978088</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1824189760240353</v>
+        <v>0.07781329933981386</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="S10" s="16">
-        <v>0.09223916600712044</v>
+        <v>0.1100485432047497</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1772501371084851</v>
+        <v>0.1216897447968387</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D11" s="10">
-        <v>0.06198862707716482</v>
+        <v>0.08405044852636091</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="G11" s="12">
-        <v>0.02410745132445478</v>
+        <v>0.08682237222106487</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J11" s="14">
-        <v>0.04413899750636176</v>
+        <v>0.07479147359951022</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>85</v>
+        <v>224</v>
       </c>
       <c r="M11" s="16">
-        <v>0.06061069036621609</v>
+        <v>0.05284340337794348</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="P11" s="18">
-        <v>0.1336082025458386</v>
+        <v>0.06620575058301921</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="S11" s="16">
-        <v>0.05068645175219422</v>
+        <v>0.08958427265668464</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="V11" s="18">
-        <v>0.07063850019368005</v>
+        <v>0.08934081483479041</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D12" s="10">
-        <v>0.04494704554243651</v>
+        <v>0.0565024211382195</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="G12" s="12">
-        <v>0.02274497848658994</v>
+        <v>0.08174777230581423</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="J12" s="14">
-        <v>0.03623756938427299</v>
+        <v>0.04819929130345577</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02308444204774514</v>
+        <v>0.04415373474168698</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="P12" s="18">
-        <v>0.07115355527242989</v>
+        <v>0.01450494306749575</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01804828827313737</v>
+        <v>0.04935376816869518</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="V12" s="18">
-        <v>0.06663214183580719</v>
+        <v>0.03855573327444127</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0.015711563972781</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.02646180208561456</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0.03024426919347724</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.01809654744238372</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>192</v>
-      </c>
       <c r="I13" s="13" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03421203363407589</v>
+        <v>0.02835257848397214</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02099629684256171</v>
+        <v>0.03366979732620657</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01223417272496692</v>
+        <v>0.01140231194022031</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01694744805227791</v>
+        <v>0.02590359023847002</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="V13" s="18">
-        <v>0.003157986196476193</v>
+        <v>0.02798104315354953</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3352,7 +3319,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3361,7 +3328,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3370,7 +3337,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3379,7 +3346,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3388,7 +3355,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3397,7 +3364,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3406,7 +3373,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3415,331 +3382,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2030705596591913</v>
+        <v>0.1755184039234016</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="G16" s="12">
-        <v>0.3410486543992513</v>
+        <v>0.1449976967809643</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1700008209113582</v>
+        <v>0.172734915882198</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="M16" s="16">
-        <v>0.4715631140423368</v>
+        <v>0.2263039055572165</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="P16" s="18">
-        <v>0.08834182655535923</v>
+        <v>0.2812893370207775</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="S16" s="16">
-        <v>0.3814038627973423</v>
+        <v>0.2383465656597275</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="V16" s="18">
-        <v>0.03470035729298841</v>
+        <v>0.1716420316198993</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1770575649901509</v>
+        <v>0.09875694268221701</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1686118737597452</v>
+        <v>0.1249554669111399</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1139656644096261</v>
+        <v>0.1326855613803522</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="M17" s="16">
-        <v>0.06594032692497748</v>
+        <v>0.07141075619399817</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="P17" s="18">
-        <v>0.07984986656695049</v>
+        <v>0.02924444818134237</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1769728806967135</v>
+        <v>0.1288514974229917</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="V17" s="18">
-        <v>0.01540501752795585</v>
+        <v>0.09611340692777606</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05401158868435631</v>
+        <v>0.06512984557181571</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="G18" s="12">
-        <v>0.03050553352585112</v>
+        <v>0.1150081604533852</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="J18" s="14">
-        <v>0.1117995295678709</v>
+        <v>0.03236049047190283</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M18" s="16">
-        <v>0.04515927079401885</v>
+        <v>0.05365734602225546</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01583354995333992</v>
+        <v>0.02524138554446622</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02574745250568451</v>
+        <v>0.06085065387751629</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="V18" s="18">
-        <v>0.008660430359273687</v>
+        <v>0.05978533879354978</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D19" s="10">
-        <v>0.0160449988573268</v>
+        <v>0.04357196217807788</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02833998980355686</v>
+        <v>0.0692362577840963</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="J19" s="14">
-        <v>0.06735013671800309</v>
+        <v>0.03006695315822545</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03628795951401921</v>
+        <v>0.04798867164128435</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01136317111258403</v>
+        <v>0.02389947705309243</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01386353538870699</v>
+        <v>0.05829642396393758</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="V19" s="18">
-        <v>0.003336758902687439</v>
+        <v>0.05666819735120109</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D20" s="10">
-        <v>0.004697878185796308</v>
+        <v>0.02929245932784407</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="G20" s="12">
-        <v>0.02818877018051354</v>
+        <v>0.03658746227422617</v>
       </c>
       <c r="H20" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.02667252946974999</v>
+      </c>
+      <c r="K20" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.03989698993222464</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>190</v>
-      </c>
       <c r="L20" s="15" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02375611813583206</v>
+        <v>0.0153222774032093</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="P20" s="18">
-        <v>0.003811911924809144</v>
+        <v>0.0151374058909012</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="S20" s="16">
-        <v>0.004205654533389722</v>
+        <v>0.02387297392425507</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>192</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="V20" s="18">
-        <v>0.001910185205220767</v>
+        <v>0.03540632674736222</v>
       </c>
     </row>
   </sheetData>
